--- a/main/ig/ValueSet-fr-doc-vs-savoir-faire-profession-medecin.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-savoir-faire-profession-medecin.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-savoir-faire-profession-medecin.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-savoir-faire-profession-medecin.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-doc-vs-savoir-faire-profession-medecin.xlsx
+++ b/main/ig/ValueSet-fr-doc-vs-savoir-faire-profession-medecin.xlsx
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
